--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/48.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/48.xlsx
@@ -426,13 +426,13 @@
         <v>-19.58403335920618</v>
       </c>
       <c r="E2">
-        <v>-17.21920022143406</v>
+        <v>-18.27350122266443</v>
       </c>
       <c r="F2">
-        <v>0.7362519719932901</v>
+        <v>0.117446611488809</v>
       </c>
       <c r="G2">
-        <v>-16.28269132168626</v>
+        <v>-16.88019416104222</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.2230784883958</v>
       </c>
       <c r="E3">
-        <v>-17.86851743316907</v>
+        <v>-17.26385554959861</v>
       </c>
       <c r="F3">
-        <v>1.39775801537728</v>
+        <v>0.1279527952585151</v>
       </c>
       <c r="G3">
-        <v>-15.43018269902101</v>
+        <v>-16.82309978757916</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.65106746300841</v>
       </c>
       <c r="E4">
-        <v>-16.9606669696748</v>
+        <v>-18.56687161101635</v>
       </c>
       <c r="F4">
-        <v>1.354114650393385</v>
+        <v>-0.2585510093766922</v>
       </c>
       <c r="G4">
-        <v>-15.62532933034525</v>
+        <v>-16.21740573706859</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.9043058557671</v>
       </c>
       <c r="E5">
-        <v>-19.20054782890206</v>
+        <v>-17.46909479363767</v>
       </c>
       <c r="F5">
-        <v>0.6136453127049352</v>
+        <v>0.2878666372667513</v>
       </c>
       <c r="G5">
-        <v>-14.84721909629296</v>
+        <v>-16.27391921986012</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.99238622275117</v>
       </c>
       <c r="E6">
-        <v>-20.17178460363586</v>
+        <v>-19.21414128956822</v>
       </c>
       <c r="F6">
-        <v>1.295860541158913</v>
+        <v>0.319830021871173</v>
       </c>
       <c r="G6">
-        <v>-15.77636221031345</v>
+        <v>-15.4991964269148</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.95909784162599</v>
       </c>
       <c r="E7">
-        <v>-20.08947210838909</v>
+        <v>-20.54040287477102</v>
       </c>
       <c r="F7">
-        <v>1.521067130223209</v>
+        <v>0.2551751177152687</v>
       </c>
       <c r="G7">
-        <v>-15.2255982259999</v>
+        <v>-15.13431745748851</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.8154881466311</v>
       </c>
       <c r="E8">
-        <v>-21.71266338404918</v>
+        <v>-20.04332993057024</v>
       </c>
       <c r="F8">
-        <v>1.700779781525756</v>
+        <v>0.3622722541210084</v>
       </c>
       <c r="G8">
-        <v>-13.93365821136453</v>
+        <v>-15.05292618948826</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.59870731096348</v>
       </c>
       <c r="E9">
-        <v>-18.44454707786617</v>
+        <v>-20.78595734114018</v>
       </c>
       <c r="F9">
-        <v>1.787861076377651</v>
+        <v>0.3899620912943875</v>
       </c>
       <c r="G9">
-        <v>-14.07857150601116</v>
+        <v>-15.09416812179407</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.32464558487389</v>
       </c>
       <c r="E10">
-        <v>-22.72057716799254</v>
+        <v>-22.02935405399</v>
       </c>
       <c r="F10">
-        <v>2.204133920367264</v>
+        <v>0.2822088879056306</v>
       </c>
       <c r="G10">
-        <v>-13.27323381661815</v>
+        <v>-14.7616284456179</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.01765005667074</v>
       </c>
       <c r="E11">
-        <v>-21.462556998068</v>
+        <v>-21.69472566433724</v>
       </c>
       <c r="F11">
-        <v>1.91670037200467</v>
+        <v>0.913217756988154</v>
       </c>
       <c r="G11">
-        <v>-13.87892264563955</v>
+        <v>-13.71470681085852</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.709233465110128</v>
       </c>
       <c r="E12">
-        <v>-21.79938658972292</v>
+        <v>-23.77377341501051</v>
       </c>
       <c r="F12">
-        <v>2.280173077739842</v>
+        <v>0.8814067919858474</v>
       </c>
       <c r="G12">
-        <v>-12.39051887903372</v>
+        <v>-13.72699036415971</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.412280883183625</v>
       </c>
       <c r="E13">
-        <v>-24.70765620708881</v>
+        <v>-24.35668908408417</v>
       </c>
       <c r="F13">
-        <v>1.767211533760665</v>
+        <v>1.166166370372205</v>
       </c>
       <c r="G13">
-        <v>-12.30061919441103</v>
+        <v>-12.91491434297703</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.171270971888069</v>
       </c>
       <c r="E14">
-        <v>-24.94463844528352</v>
+        <v>-24.61341984212845</v>
       </c>
       <c r="F14">
-        <v>2.323483439027811</v>
+        <v>1.234148826385155</v>
       </c>
       <c r="G14">
-        <v>-11.15048046686969</v>
+        <v>-12.96105925362496</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.994067749426103</v>
       </c>
       <c r="E15">
-        <v>-24.70027179735326</v>
+        <v>-25.83504957442484</v>
       </c>
       <c r="F15">
-        <v>2.167881249351147</v>
+        <v>1.772140319807322</v>
       </c>
       <c r="G15">
-        <v>-11.10260593793015</v>
+        <v>-11.26906048619806</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.903472226784634</v>
       </c>
       <c r="E16">
-        <v>-25.48604692037685</v>
+        <v>-27.13514592828122</v>
       </c>
       <c r="F16">
-        <v>2.529399008015713</v>
+        <v>1.481633528380341</v>
       </c>
       <c r="G16">
-        <v>-10.29488855484234</v>
+        <v>-11.42346253206109</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.900858164389558</v>
       </c>
       <c r="E17">
-        <v>-27.87950107476229</v>
+        <v>-26.93076639898641</v>
       </c>
       <c r="F17">
-        <v>3.145689445085294</v>
+        <v>1.942832050093383</v>
       </c>
       <c r="G17">
-        <v>-8.740677054700623</v>
+        <v>-10.38259129789161</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.980445991120702</v>
       </c>
       <c r="E18">
-        <v>-27.11870751785755</v>
+        <v>-28.66130157454801</v>
       </c>
       <c r="F18">
-        <v>3.063641310572809</v>
+        <v>2.256215035716075</v>
       </c>
       <c r="G18">
-        <v>-9.237191071783139</v>
+        <v>-10.19663840364498</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.143982911647369</v>
       </c>
       <c r="E19">
-        <v>-28.60130428374954</v>
+        <v>-28.46713479190095</v>
       </c>
       <c r="F19">
-        <v>3.386020366189904</v>
+        <v>2.454259457642575</v>
       </c>
       <c r="G19">
-        <v>-8.020336071588192</v>
+        <v>-8.987568643820728</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.372896083462154</v>
       </c>
       <c r="E20">
-        <v>-28.62159272107133</v>
+        <v>-29.86092344003414</v>
       </c>
       <c r="F20">
-        <v>3.914485634479876</v>
+        <v>2.418755630758588</v>
       </c>
       <c r="G20">
-        <v>-8.539983896492561</v>
+        <v>-9.194223437302595</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6751181946932692</v>
       </c>
       <c r="E21">
-        <v>-30.04520973293943</v>
+        <v>-30.99695964013714</v>
       </c>
       <c r="F21">
-        <v>3.483976468305751</v>
+        <v>2.705967176657233</v>
       </c>
       <c r="G21">
-        <v>-7.94694412501511</v>
+        <v>-8.564784664735843</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.04046672320268916</v>
       </c>
       <c r="E22">
-        <v>-30.58194999850365</v>
+        <v>-31.57087114705857</v>
       </c>
       <c r="F22">
-        <v>4.64525644661635</v>
+        <v>2.927162810757173</v>
       </c>
       <c r="G22">
-        <v>-7.902359134260373</v>
+        <v>-7.492401743351627</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.5254372022344597</v>
       </c>
       <c r="E23">
-        <v>-29.98504631368796</v>
+        <v>-32.87269523682608</v>
       </c>
       <c r="F23">
-        <v>4.155179380506912</v>
+        <v>2.507906187382677</v>
       </c>
       <c r="G23">
-        <v>-6.24236156865904</v>
+        <v>-7.381857595874709</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.020412933944418</v>
       </c>
       <c r="E24">
-        <v>-33.01319214612804</v>
+        <v>-31.83948008949186</v>
       </c>
       <c r="F24">
-        <v>3.378621388548098</v>
+        <v>2.570292193222313</v>
       </c>
       <c r="G24">
-        <v>-6.776352824346986</v>
+        <v>-6.171928901079985</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.441788698789505</v>
       </c>
       <c r="E25">
-        <v>-32.71874399943734</v>
+        <v>-32.76925743217556</v>
       </c>
       <c r="F25">
-        <v>4.584258784543805</v>
+        <v>2.604815233101385</v>
       </c>
       <c r="G25">
-        <v>-6.552724274905995</v>
+        <v>-6.413010278112568</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.779043835735194</v>
       </c>
       <c r="E26">
-        <v>-32.5590904028996</v>
+        <v>-33.42785084140458</v>
       </c>
       <c r="F26">
-        <v>4.151846030078047</v>
+        <v>2.864748640425842</v>
       </c>
       <c r="G26">
-        <v>-6.63359469936032</v>
+        <v>-6.449106432829301</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.027882173431648</v>
       </c>
       <c r="E27">
-        <v>-30.85580860005152</v>
+        <v>-33.92201446107232</v>
       </c>
       <c r="F27">
-        <v>4.943770237358791</v>
+        <v>2.841184901285807</v>
       </c>
       <c r="G27">
-        <v>-6.439167328170933</v>
+        <v>-6.852962513628615</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.176529202039283</v>
       </c>
       <c r="E28">
-        <v>-32.67021164850105</v>
+        <v>-33.68316535438709</v>
       </c>
       <c r="F28">
-        <v>4.346041857051141</v>
+        <v>2.802551502354044</v>
       </c>
       <c r="G28">
-        <v>-5.143044900700604</v>
+        <v>-6.513158440627674</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.219683518884875</v>
       </c>
       <c r="E29">
-        <v>-31.6264784934867</v>
+        <v>-34.14346576551784</v>
       </c>
       <c r="F29">
-        <v>3.72264734113515</v>
+        <v>2.454140172736572</v>
       </c>
       <c r="G29">
-        <v>-5.500842225423497</v>
+        <v>-6.160329362861669</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.150986884565365</v>
       </c>
       <c r="E30">
-        <v>-32.43916850250084</v>
+        <v>-33.606864632533</v>
       </c>
       <c r="F30">
-        <v>3.518830855145943</v>
+        <v>2.655773082252</v>
       </c>
       <c r="G30">
-        <v>-6.180009155589481</v>
+        <v>-5.876371727409232</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.969069793776063</v>
       </c>
       <c r="E31">
-        <v>-30.7317127222713</v>
+        <v>-33.9395742385537</v>
       </c>
       <c r="F31">
-        <v>3.705611137129175</v>
+        <v>2.868883850500617</v>
       </c>
       <c r="G31">
-        <v>-6.331536771657696</v>
+        <v>-5.638814855574652</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.676279459181499</v>
       </c>
       <c r="E32">
-        <v>-31.42141576092896</v>
+        <v>-33.13306836120223</v>
       </c>
       <c r="F32">
-        <v>3.398528713972176</v>
+        <v>2.67744483024404</v>
       </c>
       <c r="G32">
-        <v>-6.136018109229222</v>
+        <v>-5.796417674306388</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.287235540348237</v>
       </c>
       <c r="E33">
-        <v>-30.27608259727532</v>
+        <v>-34.43785576725</v>
       </c>
       <c r="F33">
-        <v>3.494587854735613</v>
+        <v>2.745085998887037</v>
       </c>
       <c r="G33">
-        <v>-6.036781096576415</v>
+        <v>-5.840894319160594</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.8171768441506</v>
       </c>
       <c r="E34">
-        <v>-31.52583787666346</v>
+        <v>-32.14579603754326</v>
       </c>
       <c r="F34">
-        <v>3.252810604145715</v>
+        <v>2.148782410512201</v>
       </c>
       <c r="G34">
-        <v>-6.145949381653817</v>
+        <v>-5.58060569417119</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.2886670558818302</v>
       </c>
       <c r="E35">
-        <v>-29.67143109673317</v>
+        <v>-31.64710749413712</v>
       </c>
       <c r="F35">
-        <v>3.819929152185118</v>
+        <v>3.065821573576977</v>
       </c>
       <c r="G35">
-        <v>-6.565347225004029</v>
+        <v>-5.882000492747673</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.2759083503428668</v>
       </c>
       <c r="E36">
-        <v>-31.38475951777602</v>
+        <v>-33.30024342344922</v>
       </c>
       <c r="F36">
-        <v>3.677436705025159</v>
+        <v>2.294528684830357</v>
       </c>
       <c r="G36">
-        <v>-6.837224945233384</v>
+        <v>-5.902406072471813</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.8505088519966535</v>
       </c>
       <c r="E37">
-        <v>-31.12544961549902</v>
+        <v>-32.00955409324359</v>
       </c>
       <c r="F37">
-        <v>3.461511144341828</v>
+        <v>3.047925524206897</v>
       </c>
       <c r="G37">
-        <v>-5.639404883852244</v>
+        <v>-6.252739278408715</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.406365784018271</v>
       </c>
       <c r="E38">
-        <v>-29.95419418336148</v>
+        <v>-31.2903881734476</v>
       </c>
       <c r="F38">
-        <v>4.00925086536014</v>
+        <v>2.825898209234545</v>
       </c>
       <c r="G38">
-        <v>-6.476247733598514</v>
+        <v>-5.969750229199581</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.922103607328972</v>
       </c>
       <c r="E39">
-        <v>-27.68684190782614</v>
+        <v>-31.39954287348674</v>
       </c>
       <c r="F39">
-        <v>4.032350718754607</v>
+        <v>2.767458545701846</v>
       </c>
       <c r="G39">
-        <v>-7.371803618454331</v>
+        <v>-6.04157703439029</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.373059501121571</v>
       </c>
       <c r="E40">
-        <v>-28.71702313428758</v>
+        <v>-30.74856645382746</v>
       </c>
       <c r="F40">
-        <v>4.39558982488219</v>
+        <v>3.109430147129955</v>
       </c>
       <c r="G40">
-        <v>-5.98058220850811</v>
+        <v>-5.81089164231952</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.749711906554621</v>
       </c>
       <c r="E41">
-        <v>-29.89407644943458</v>
+        <v>-29.85724369480034</v>
       </c>
       <c r="F41">
-        <v>4.470512342995794</v>
+        <v>3.141287500706818</v>
       </c>
       <c r="G41">
-        <v>-6.582102983789794</v>
+        <v>-5.434276070583882</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.043566534609634</v>
       </c>
       <c r="E42">
-        <v>-25.66453948348401</v>
+        <v>-29.58138739860523</v>
       </c>
       <c r="F42">
-        <v>4.416088604631867</v>
+        <v>3.013974057835756</v>
       </c>
       <c r="G42">
-        <v>-7.162672533727792</v>
+        <v>-6.477944717582738</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.257894107144876</v>
       </c>
       <c r="E43">
-        <v>-25.94819551054714</v>
+        <v>-29.64171694630969</v>
       </c>
       <c r="F43">
-        <v>4.235791125942943</v>
+        <v>3.156524490713912</v>
       </c>
       <c r="G43">
-        <v>-7.350567821950215</v>
+        <v>-5.814536241768714</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.40156312602445</v>
       </c>
       <c r="E44">
-        <v>-26.78328586484174</v>
+        <v>-28.47614726047583</v>
       </c>
       <c r="F44">
-        <v>4.378209020036651</v>
+        <v>3.207149336168601</v>
       </c>
       <c r="G44">
-        <v>-6.606051343924076</v>
+        <v>-6.218627289581228</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.485011186972629</v>
       </c>
       <c r="E45">
-        <v>-26.14280253359464</v>
+        <v>-28.07206471783796</v>
       </c>
       <c r="F45">
-        <v>4.677761583502202</v>
+        <v>3.063376233003913</v>
       </c>
       <c r="G45">
-        <v>-6.800674520957798</v>
+        <v>-5.677553083817591</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.525537619912343</v>
       </c>
       <c r="E46">
-        <v>-28.102648966034</v>
+        <v>-27.74017329444827</v>
       </c>
       <c r="F46">
-        <v>4.793111744342034</v>
+        <v>3.720298091180811</v>
       </c>
       <c r="G46">
-        <v>-7.845490590204448</v>
+        <v>-5.93192054007435</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.534496511807091</v>
       </c>
       <c r="E47">
-        <v>-25.965684683436</v>
+        <v>-26.61942506523196</v>
       </c>
       <c r="F47">
-        <v>4.157734065577146</v>
+        <v>4.040702318909632</v>
       </c>
       <c r="G47">
-        <v>-7.720713968589076</v>
+        <v>-6.49504509465453</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.526475597317828</v>
       </c>
       <c r="E48">
-        <v>-23.99199144443965</v>
+        <v>-25.91785630181927</v>
       </c>
       <c r="F48">
-        <v>4.13533004080103</v>
+        <v>3.614240555865584</v>
       </c>
       <c r="G48">
-        <v>-6.660028488345342</v>
+        <v>-6.085675121278785</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.510409512331176</v>
       </c>
       <c r="E49">
-        <v>-24.52608196117863</v>
+        <v>-25.8959148863902</v>
       </c>
       <c r="F49">
-        <v>3.763520645524083</v>
+        <v>3.816696862579395</v>
       </c>
       <c r="G49">
-        <v>-7.924926410505956</v>
+        <v>-6.490544170979451</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.492133963074761</v>
       </c>
       <c r="E50">
-        <v>-23.50539289920009</v>
+        <v>-24.52334499491557</v>
       </c>
       <c r="F50">
-        <v>5.040553371232274</v>
+        <v>3.809249839628227</v>
       </c>
       <c r="G50">
-        <v>-5.888253226043389</v>
+        <v>-6.651916904900753</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.477734092765616</v>
       </c>
       <c r="E51">
-        <v>-22.99103428946538</v>
+        <v>-24.5775485559159</v>
       </c>
       <c r="F51">
-        <v>4.201856226919858</v>
+        <v>3.840601889089383</v>
       </c>
       <c r="G51">
-        <v>-8.095025558223055</v>
+        <v>-5.890198230763768</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.46853211614166</v>
       </c>
       <c r="E52">
-        <v>-22.66690521804178</v>
+        <v>-24.38818703877167</v>
       </c>
       <c r="F52">
-        <v>4.507691128768242</v>
+        <v>4.077824775698689</v>
       </c>
       <c r="G52">
-        <v>-8.018951071582606</v>
+        <v>-7.321964504209978</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.471342209301294</v>
       </c>
       <c r="E53">
-        <v>-22.70055868940687</v>
+        <v>-23.46032224990305</v>
       </c>
       <c r="F53">
-        <v>4.745531977460035</v>
+        <v>4.034761267896753</v>
       </c>
       <c r="G53">
-        <v>-7.974988743412849</v>
+        <v>-6.864415850149829</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.490975122463222</v>
       </c>
       <c r="E54">
-        <v>-20.8322282685101</v>
+        <v>-22.57113631810256</v>
       </c>
       <c r="F54">
-        <v>4.789907619228005</v>
+        <v>3.96623043266315</v>
       </c>
       <c r="G54">
-        <v>-7.706002422818152</v>
+        <v>-7.259113438923517</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.537480012963667</v>
       </c>
       <c r="E55">
-        <v>-19.8251451268317</v>
+        <v>-21.79530398299061</v>
       </c>
       <c r="F55">
-        <v>4.401423188132704</v>
+        <v>4.186249785051116</v>
       </c>
       <c r="G55">
-        <v>-7.756342800023998</v>
+        <v>-7.320596474044235</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.621477376530391</v>
       </c>
       <c r="E56">
-        <v>-19.31125582997669</v>
+        <v>-22.25152594060038</v>
       </c>
       <c r="F56">
-        <v>5.076307365071906</v>
+        <v>4.255690167692992</v>
       </c>
       <c r="G56">
-        <v>-8.354931709129861</v>
+        <v>-7.257520884722938</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.751055400297773</v>
       </c>
       <c r="E57">
-        <v>-20.65177954286895</v>
+        <v>-21.20565180514808</v>
       </c>
       <c r="F57">
-        <v>4.65847719036503</v>
+        <v>4.086396721582858</v>
       </c>
       <c r="G57">
-        <v>-8.054261392177413</v>
+        <v>-7.901048540475634</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.938905019898388</v>
       </c>
       <c r="E58">
-        <v>-20.47586612399451</v>
+        <v>-20.84338794733991</v>
       </c>
       <c r="F58">
-        <v>4.23229872897274</v>
+        <v>4.034481279714607</v>
       </c>
       <c r="G58">
-        <v>-9.137645991268579</v>
+        <v>-8.04490839967975</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.188070733318239</v>
       </c>
       <c r="E59">
-        <v>-18.12347061676633</v>
+        <v>-20.07367744572077</v>
       </c>
       <c r="F59">
-        <v>4.325453613621962</v>
+        <v>3.972688384935375</v>
       </c>
       <c r="G59">
-        <v>-9.362880148633105</v>
+        <v>-8.149142377479947</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.507736586412383</v>
       </c>
       <c r="E60">
-        <v>-18.93931083657034</v>
+        <v>-20.44806868059743</v>
       </c>
       <c r="F60">
-        <v>4.567144714001968</v>
+        <v>4.380836601438331</v>
       </c>
       <c r="G60">
-        <v>-8.566318477183122</v>
+        <v>-7.885944077643749</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.895266621448377</v>
       </c>
       <c r="E61">
-        <v>-18.59414990299782</v>
+        <v>-18.77211500826672</v>
       </c>
       <c r="F61">
-        <v>5.054706856676506</v>
+        <v>3.86236144402612</v>
       </c>
       <c r="G61">
-        <v>-9.402828456994024</v>
+        <v>-8.44010202992575</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.350458380835902</v>
       </c>
       <c r="E62">
-        <v>-18.13085087329054</v>
+        <v>-18.57668980258824</v>
       </c>
       <c r="F62">
-        <v>4.27092218749567</v>
+        <v>4.177417731802468</v>
       </c>
       <c r="G62">
-        <v>-8.787370221712683</v>
+        <v>-8.552310527079504</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.866895173602644</v>
       </c>
       <c r="E63">
-        <v>-17.03255490449626</v>
+        <v>-18.50676633672343</v>
       </c>
       <c r="F63">
-        <v>4.039199660440953</v>
+        <v>4.144904311242587</v>
       </c>
       <c r="G63">
-        <v>-8.814234783555239</v>
+        <v>-8.90618520805425</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.43110217041266</v>
       </c>
       <c r="E64">
-        <v>-17.01657750052965</v>
+        <v>-18.62959756165523</v>
       </c>
       <c r="F64">
-        <v>5.125916632090763</v>
+        <v>3.698243637448677</v>
       </c>
       <c r="G64">
-        <v>-9.336014281418255</v>
+        <v>-8.880250071286129</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.035252053304664</v>
       </c>
       <c r="E65">
-        <v>-18.24439967091136</v>
+        <v>-18.22460961894855</v>
       </c>
       <c r="F65">
-        <v>4.388469178687726</v>
+        <v>4.043730830134266</v>
       </c>
       <c r="G65">
-        <v>-9.355393838518088</v>
+        <v>-8.903953021428848</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.657023386450593</v>
       </c>
       <c r="E66">
-        <v>-17.91030289230817</v>
+        <v>-17.40980770197574</v>
       </c>
       <c r="F66">
-        <v>4.906576540973093</v>
+        <v>3.801744830958864</v>
       </c>
       <c r="G66">
-        <v>-9.555466944885758</v>
+        <v>-8.909513907407918</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.285485056896853</v>
       </c>
       <c r="E67">
-        <v>-15.47811588910738</v>
+        <v>-18.21950532223034</v>
       </c>
       <c r="F67">
-        <v>4.419506448535818</v>
+        <v>4.466494761092217</v>
       </c>
       <c r="G67">
-        <v>-9.278759347162843</v>
+        <v>-9.381024823541342</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.899248484345019</v>
       </c>
       <c r="E68">
-        <v>-15.74709446734858</v>
+        <v>-17.24853019980999</v>
       </c>
       <c r="F68">
-        <v>4.673359639123726</v>
+        <v>3.67139790665875</v>
       </c>
       <c r="G68">
-        <v>-9.854217059191443</v>
+        <v>-9.609326605800426</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.48417775117148</v>
       </c>
       <c r="E69">
-        <v>-18.68176189589508</v>
+        <v>-17.75645548520255</v>
       </c>
       <c r="F69">
-        <v>4.105416037151135</v>
+        <v>3.928289548880127</v>
       </c>
       <c r="G69">
-        <v>-9.194675096116859</v>
+        <v>-9.316543348257731</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.02680771003278</v>
       </c>
       <c r="E70">
-        <v>-16.26629156827672</v>
+        <v>-17.27249422915425</v>
       </c>
       <c r="F70">
-        <v>4.785807200584148</v>
+        <v>3.763446092457831</v>
       </c>
       <c r="G70">
-        <v>-9.921486809698363</v>
+        <v>-9.245588531760454</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.51087608094223</v>
       </c>
       <c r="E71">
-        <v>-17.7963761524568</v>
+        <v>-16.59377643445077</v>
       </c>
       <c r="F71">
-        <v>4.16579573714119</v>
+        <v>3.627325447360205</v>
       </c>
       <c r="G71">
-        <v>-9.791888142823204</v>
+        <v>-9.254415459223008</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.93249534448094</v>
       </c>
       <c r="E72">
-        <v>-15.35884811949228</v>
+        <v>-17.25243421845533</v>
       </c>
       <c r="F72">
-        <v>4.336275405372135</v>
+        <v>3.544735560566289</v>
       </c>
       <c r="G72">
-        <v>-9.388491553071926</v>
+        <v>-8.86103107497865</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.27900783740434</v>
       </c>
       <c r="E73">
-        <v>-13.6483065032484</v>
+        <v>-16.99892635239912</v>
       </c>
       <c r="F73">
-        <v>3.560469571015063</v>
+        <v>3.669389944074364</v>
       </c>
       <c r="G73">
-        <v>-8.857968671573273</v>
+        <v>-9.288909922133092</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.54977019767686</v>
       </c>
       <c r="E74">
-        <v>-16.46616901649542</v>
+        <v>-16.97676481676984</v>
       </c>
       <c r="F74">
-        <v>3.097388998562861</v>
+        <v>3.331329893522275</v>
       </c>
       <c r="G74">
-        <v>-9.299445581930531</v>
+        <v>-9.13311896014759</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.74132474887592</v>
       </c>
       <c r="E75">
-        <v>-15.11848101406783</v>
+        <v>-17.74595616697339</v>
       </c>
       <c r="F75">
-        <v>4.080992452646994</v>
+        <v>3.233889035930969</v>
       </c>
       <c r="G75">
-        <v>-8.768661625972765</v>
+        <v>-8.957051650295204</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.85138438502708</v>
       </c>
       <c r="E76">
-        <v>-17.66589471226467</v>
+        <v>-17.22822514964291</v>
       </c>
       <c r="F76">
-        <v>4.152682681154874</v>
+        <v>2.864983896768237</v>
       </c>
       <c r="G76">
-        <v>-8.717049816151047</v>
+        <v>-9.125294558608022</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.88339180134572</v>
       </c>
       <c r="E77">
-        <v>-16.64069526278736</v>
+        <v>-17.60287803683304</v>
       </c>
       <c r="F77">
-        <v>3.434693578043597</v>
+        <v>2.68138620234656</v>
       </c>
       <c r="G77">
-        <v>-8.969427885029377</v>
+        <v>-8.426637114697083</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.83486639285737</v>
       </c>
       <c r="E78">
-        <v>-16.97877912426238</v>
+        <v>-16.71904974764158</v>
       </c>
       <c r="F78">
-        <v>3.934719336660657</v>
+        <v>2.87399487737589</v>
       </c>
       <c r="G78">
-        <v>-8.761312379948782</v>
+        <v>-8.343227741127901</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.71058362911369</v>
       </c>
       <c r="E79">
-        <v>-17.00584975567761</v>
+        <v>-17.90255715318737</v>
       </c>
       <c r="F79">
-        <v>4.410851665911368</v>
+        <v>3.007101921862132</v>
       </c>
       <c r="G79">
-        <v>-8.175110148555456</v>
+        <v>-8.112907853299886</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.51264121178206</v>
       </c>
       <c r="E80">
-        <v>-20.05356344327462</v>
+        <v>-17.4525400932969</v>
       </c>
       <c r="F80">
-        <v>3.398790478071461</v>
+        <v>2.755157289770273</v>
       </c>
       <c r="G80">
-        <v>-8.985530957667365</v>
+        <v>-8.387739631034087</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.24238845101118</v>
       </c>
       <c r="E81">
-        <v>-19.39624714652798</v>
+        <v>-18.7543641830644</v>
       </c>
       <c r="F81">
-        <v>3.336353113452851</v>
+        <v>2.837869774939804</v>
       </c>
       <c r="G81">
-        <v>-7.754369077113116</v>
+        <v>-8.445669442766299</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.90843326531318</v>
       </c>
       <c r="E82">
-        <v>-19.05755691619954</v>
+        <v>-18.84462177157558</v>
       </c>
       <c r="F82">
-        <v>3.923804767761371</v>
+        <v>3.175036845431675</v>
       </c>
       <c r="G82">
-        <v>-7.215532279464063</v>
+        <v>-7.3099133071774</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.50943460364958</v>
       </c>
       <c r="E83">
-        <v>-20.2362756690878</v>
+        <v>-20.48595427430252</v>
       </c>
       <c r="F83">
-        <v>3.196715220362938</v>
+        <v>2.54877949177161</v>
       </c>
       <c r="G83">
-        <v>-7.212120036283478</v>
+        <v>-7.916876179559258</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.05292580643413</v>
       </c>
       <c r="E84">
-        <v>-21.2052863225515</v>
+        <v>-21.39289933772798</v>
       </c>
       <c r="F84">
-        <v>3.335380610121964</v>
+        <v>2.482327858719033</v>
       </c>
       <c r="G84">
-        <v>-7.530194882052583</v>
+        <v>-7.503369481378894</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.541322760055044</v>
       </c>
       <c r="E85">
-        <v>-21.91071341928495</v>
+        <v>-21.50621970872592</v>
       </c>
       <c r="F85">
-        <v>3.583042582741349</v>
+        <v>2.51637872917851</v>
       </c>
       <c r="G85">
-        <v>-7.104199687120628</v>
+        <v>-7.838243163219517</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.979793248036124</v>
       </c>
       <c r="E86">
-        <v>-22.68531225063342</v>
+        <v>-23.02376990112768</v>
       </c>
       <c r="F86">
-        <v>3.450505455028234</v>
+        <v>2.615259289315881</v>
       </c>
       <c r="G86">
-        <v>-6.655070684366819</v>
+        <v>-7.003531986431891</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.381965242660762</v>
       </c>
       <c r="E87">
-        <v>-23.84698622424459</v>
+        <v>-23.27994828206575</v>
       </c>
       <c r="F87">
-        <v>3.278973760195735</v>
+        <v>2.254727287860647</v>
       </c>
       <c r="G87">
-        <v>-5.280169038859647</v>
+        <v>-6.400878147997664</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.75326531769586</v>
       </c>
       <c r="E88">
-        <v>-25.09001745449782</v>
+        <v>-25.08558597801423</v>
       </c>
       <c r="F88">
-        <v>3.569150861396402</v>
+        <v>2.318625892577795</v>
       </c>
       <c r="G88">
-        <v>-5.985286770261296</v>
+        <v>-6.648690024586138</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.115280183869577</v>
       </c>
       <c r="E89">
-        <v>-26.43205708952364</v>
+        <v>-26.29515893783465</v>
       </c>
       <c r="F89">
-        <v>2.398351284892831</v>
+        <v>2.015961981147329</v>
       </c>
       <c r="G89">
-        <v>-6.242257138875395</v>
+        <v>-6.679752663731204</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.477851864470482</v>
       </c>
       <c r="E90">
-        <v>-27.63119718249609</v>
+        <v>-28.54148558103804</v>
       </c>
       <c r="F90">
-        <v>3.136922004494064</v>
+        <v>2.118235534166567</v>
       </c>
       <c r="G90">
-        <v>-5.318993421674093</v>
+        <v>-6.517497498138104</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.859497302916051</v>
       </c>
       <c r="E91">
-        <v>-30.41028323820885</v>
+        <v>-29.46119969268168</v>
       </c>
       <c r="F91">
-        <v>3.133875269186568</v>
+        <v>1.82119955087072</v>
       </c>
       <c r="G91">
-        <v>-5.621346363515513</v>
+        <v>-6.252264122893132</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.273383342996934</v>
       </c>
       <c r="E92">
-        <v>-30.25239475648416</v>
+        <v>-30.52785649760342</v>
       </c>
       <c r="F92">
-        <v>2.564985671639979</v>
+        <v>1.538572190179168</v>
       </c>
       <c r="G92">
-        <v>-5.637373724560358</v>
+        <v>-6.326733001610047</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.723821842330276</v>
       </c>
       <c r="E93">
-        <v>-34.08306768982652</v>
+        <v>-32.27106727412841</v>
       </c>
       <c r="F93">
-        <v>2.112516485617639</v>
+        <v>1.470985693784756</v>
       </c>
       <c r="G93">
-        <v>-5.153654966718888</v>
+        <v>-6.064159975103419</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.220044703195738</v>
       </c>
       <c r="E94">
-        <v>-33.65362148562792</v>
+        <v>-34.22874780686187</v>
       </c>
       <c r="F94">
-        <v>2.543328834261189</v>
+        <v>1.246643920288983</v>
       </c>
       <c r="G94">
-        <v>-4.836658358465913</v>
+        <v>-5.490498455353507</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.752744305009527</v>
       </c>
       <c r="E95">
-        <v>-36.30544899313661</v>
+        <v>-36.11029789940557</v>
       </c>
       <c r="F95">
-        <v>2.635637127424749</v>
+        <v>1.217442312605495</v>
       </c>
       <c r="G95">
-        <v>-5.560868465062374</v>
+        <v>-5.55206503430114</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.320267396129285</v>
       </c>
       <c r="E96">
-        <v>-38.27962815785796</v>
+        <v>-38.38833223446836</v>
       </c>
       <c r="F96">
-        <v>1.729060244657331</v>
+        <v>0.8884031830698921</v>
       </c>
       <c r="G96">
-        <v>-4.287979053708362</v>
+        <v>-5.543475684596377</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.911827238924204</v>
       </c>
       <c r="E97">
-        <v>-39.31530615950781</v>
+        <v>-40.53596819356552</v>
       </c>
       <c r="F97">
-        <v>1.501908648931262</v>
+        <v>0.6142641031548265</v>
       </c>
       <c r="G97">
-        <v>-5.70996025642708</v>
+        <v>-6.31149669617631</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.515940558465704</v>
       </c>
       <c r="E98">
-        <v>-41.24093843705323</v>
+        <v>-42.59888279484748</v>
       </c>
       <c r="F98">
-        <v>0.9879149591681966</v>
+        <v>0.5340607428483755</v>
       </c>
       <c r="G98">
-        <v>-5.057315880562217</v>
+        <v>-6.102584913995425</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.132844768113414</v>
       </c>
       <c r="E99">
-        <v>-46.16704369998141</v>
+        <v>-45.18867586140287</v>
       </c>
       <c r="F99">
-        <v>0.5135404255462261</v>
+        <v>-0.1467388057142178</v>
       </c>
       <c r="G99">
-        <v>-5.221450782260918</v>
+        <v>-6.084636044931521</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.743494903631152</v>
       </c>
       <c r="E100">
-        <v>-47.0125378486447</v>
+        <v>-46.56103705400844</v>
       </c>
       <c r="F100">
-        <v>1.180912966876842</v>
+        <v>0.08330130714541333</v>
       </c>
       <c r="G100">
-        <v>-5.169604005425999</v>
+        <v>-5.941580295061469</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.367734502833424</v>
       </c>
       <c r="E101">
-        <v>-48.75521389921161</v>
+        <v>-48.84338761394056</v>
       </c>
       <c r="F101">
-        <v>1.075208316075209</v>
+        <v>-0.3950452481729808</v>
       </c>
       <c r="G101">
-        <v>-5.675446212932562</v>
+        <v>-6.883286312054396</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.977116651349388</v>
       </c>
       <c r="E102">
-        <v>-51.32169187569225</v>
+        <v>-51.85321570783248</v>
       </c>
       <c r="F102">
-        <v>0.4075698688082938</v>
+        <v>-0.2608720948393364</v>
       </c>
       <c r="G102">
-        <v>-4.019403925386765</v>
+        <v>-6.032201850563602</v>
       </c>
     </row>
   </sheetData>
